--- a/OUTPUT/reverse_P44858_Haemophilus_influenzae_Rd_KW20.xlsx
+++ b/OUTPUT/reverse_P44858_Haemophilus_influenzae_Rd_KW20.xlsx
@@ -477,16 +477,16 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>CTG</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>CAG</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>GTC</t>
-        </is>
-      </c>
       <c r="G2" t="n">
-        <v>0.0032</v>
+        <v>0.003398640543782487</v>
       </c>
     </row>
   </sheetData>
